--- a/main/StructureDefinition-bc-merge-request-bundle.xlsx
+++ b/main/StructureDefinition-bc-merge-request-bundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-27T22:33:33+00:00</t>
+    <t>2026-03-25T22:00:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -361,7 +361,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -2269,7 +2269,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="8" hidden="true">
+    <row r="8">
       <c r="A8" t="s" s="2">
         <v>121</v>
       </c>
@@ -3857,7 +3857,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="22" hidden="true">
+    <row r="22">
       <c r="A22" t="s" s="2">
         <v>188</v>
       </c>
@@ -3971,7 +3971,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="23" hidden="true">
+    <row r="23">
       <c r="A23" t="s" s="2">
         <v>192</v>
       </c>
@@ -4765,7 +4765,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="30" hidden="true">
+    <row r="30">
       <c r="A30" t="s" s="2">
         <v>214</v>
       </c>
@@ -6913,7 +6913,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="49" hidden="true">
+    <row r="49">
       <c r="A49" t="s" s="2">
         <v>266</v>
       </c>
@@ -7481,7 +7481,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="54" hidden="true">
+    <row r="54">
       <c r="A54" t="s" s="2">
         <v>273</v>
       </c>
@@ -7595,7 +7595,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="55" hidden="true">
+    <row r="55">
       <c r="A55" t="s" s="2">
         <v>274</v>
       </c>
@@ -8389,7 +8389,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="62" hidden="true">
+    <row r="62">
       <c r="A62" t="s" s="2">
         <v>287</v>
       </c>
@@ -10537,7 +10537,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="81" hidden="true">
+    <row r="81">
       <c r="A81" t="s" s="2">
         <v>306</v>
       </c>
@@ -11105,7 +11105,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="86" hidden="true">
+    <row r="86">
       <c r="A86" t="s" s="2">
         <v>313</v>
       </c>
@@ -11219,7 +11219,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="87" hidden="true">
+    <row r="87">
       <c r="A87" t="s" s="2">
         <v>314</v>
       </c>
@@ -12015,7 +12015,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="94" hidden="true">
+    <row r="94">
       <c r="A94" t="s" s="2">
         <v>325</v>
       </c>
@@ -14281,12 +14281,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AN113">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
